--- a/shipClassTests/testResults/sensed_system_with_subsystems_test.xlsx
+++ b/shipClassTests/testResults/sensed_system_with_subsystems_test.xlsx
@@ -598,10 +598,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -637,10 +637,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -655,7 +655,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -676,10 +676,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -715,10 +715,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -733,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -751,34 +751,34 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
       <c r="K7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3">
         <f>IF(B7 = G7, 1, 0)</f>
@@ -790,13 +790,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -805,13 +805,13 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -829,10 +829,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -868,7 +868,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -883,13 +883,13 @@
         <v>2</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -907,7 +907,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -955,22 +955,22 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4">
         <v>2</v>
@@ -1006,7 +1006,7 @@
         <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1045,7 +1045,7 @@
         <v>2</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1081,10 +1081,10 @@
         <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -1102,7 +1102,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1114,22 +1114,22 @@
         <v>2</v>
       </c>
       <c r="F16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
       <c r="K16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="3">
         <f>IF(B16 = G16, 1, 0)</f>
@@ -1141,7 +1141,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>2</v>
       </c>
       <c r="F17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="3">
         <f>IF(B17 = G17, 1, 0)</f>
@@ -1180,7 +1180,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1234,10 +1234,10 @@
         <v>2</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4">
         <v>2</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="4">
         <v>2</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="4">
         <v>2</v>
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4">
         <v>2</v>
@@ -1777,7 +1777,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="K33" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="3">
         <f>IF(B33 = G33, 1, 0)</f>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" s="3">
         <f>IF(B36 = G36, 1, 0)</f>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" s="3">
         <f>IF(B37 = G37, 1, 0)</f>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="3">
         <f>IF(B49 = G49, 1, 0)</f>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="3">
         <f>IF(B50 = G50, 1, 0)</f>
@@ -2699,7 +2699,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2720,7 +2720,7 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>2</v>
@@ -2766,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4">
         <v>1</v>
@@ -2787,7 +2787,7 @@
         <v>2</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" s="4">
         <v>2</v>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
@@ -3007,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="4">
         <v>2</v>
@@ -3191,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -3212,25 +3212,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P12" s="3">
         <f>IF(B12 = I12, 1, 0)</f>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4">
         <v>1</v>
@@ -3337,7 +3337,7 @@
         <v>2</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
         <v>2</v>
@@ -3695,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -3716,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
         <v>2</v>
@@ -3741,7 +3741,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3762,25 +3762,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <f>IF(B22 = I22, 1, 0)</f>
@@ -3796,7 +3796,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3817,25 +3817,25 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
         <f>IF(B23 = I23, 1, 0)</f>
@@ -3851,7 +3851,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -3872,25 +3872,25 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <f>IF(B24 = I24, 1, 0)</f>
@@ -5064,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>1</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N48">
         <v>0</v>
@@ -5400,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -5828,25 +5828,25 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" s="3">
         <f>IF(B7 = I7, 1, 0)</f>
@@ -5871,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -5892,7 +5892,7 @@
         <v>2</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <v>2</v>
@@ -5923,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5944,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>2</v>
@@ -6302,7 +6302,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -6323,25 +6323,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" s="3">
         <f>IF(B16 = I16, 1, 0)</f>
@@ -6357,7 +6357,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -6372,31 +6372,31 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P17" s="3">
         <f>IF(B17 = I17, 1, 0)</f>
@@ -6751,7 +6751,7 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -6772,7 +6772,7 @@
         <v>2</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24">
         <v>2</v>
@@ -6916,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -6937,7 +6937,7 @@
         <v>2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>2</v>
@@ -6980,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>2</v>
@@ -7001,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="O28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3">
         <f>IF(B28 = I28, 1, 0)</f>
@@ -7237,7 +7237,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -7258,25 +7258,25 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" s="3">
         <f>IF(B33 = I33, 1, 0)</f>
@@ -7359,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -7380,7 +7380,7 @@
         <v>2</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -7402,7 +7402,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -7423,25 +7423,25 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P36" s="3">
         <f>IF(B36 = I36, 1, 0)</f>
@@ -7457,7 +7457,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -7472,31 +7472,31 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="4">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37" s="3">
         <f>IF(B37 = I37, 1, 0)</f>
@@ -7625,7 +7625,7 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -7646,7 +7646,7 @@
         <v>2</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40">
         <v>2</v>
@@ -7790,7 +7790,7 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -7811,7 +7811,7 @@
         <v>2</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -7900,7 +7900,7 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -7915,13 +7915,13 @@
         <v>1</v>
       </c>
       <c r="H45" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>2</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45">
         <v>2</v>
@@ -7936,7 +7936,7 @@
         <v>2</v>
       </c>
       <c r="O45" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P45" s="3">
         <f>IF(B45 = I45, 1, 0)</f>
@@ -8071,7 +8071,7 @@
         <v>1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -8092,7 +8092,7 @@
         <v>2</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48">
         <v>2</v>
@@ -8117,10 +8117,10 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -8138,25 +8138,25 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" s="3">
         <f>IF(B49 = I49, 1, 0)</f>
@@ -8172,7 +8172,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -8193,25 +8193,25 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P50" s="3">
         <f>IF(B50 = I50, 1, 0)</f>
@@ -8288,7 +8288,7 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -8309,7 +8309,7 @@
         <v>2</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52">
         <v>2</v>
@@ -8435,7 +8435,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -8468,7 +8468,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -8501,7 +8501,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -8534,7 +8534,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -8567,7 +8567,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -8600,7 +8600,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -8609,10 +8609,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -8621,7 +8621,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3">
         <f>IF(B8 = F8, 1, 0)</f>
@@ -8633,10 +8633,10 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -8645,10 +8645,10 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>2</v>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -8678,10 +8678,10 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -8702,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -8711,10 +8711,10 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -8843,10 +8843,10 @@
         <v>2</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>2</v>
@@ -8867,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -8876,10 +8876,10 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>2</v>
@@ -8900,7 +8900,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -8909,10 +8909,10 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>2</v>
@@ -8933,22 +8933,22 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="4">
         <v>2</v>
@@ -8966,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -8975,10 +8975,10 @@
         <v>2</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>2</v>
@@ -9002,7 +9002,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="4">
         <v>2</v>
@@ -9035,7 +9035,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="4">
         <v>2</v>
@@ -9068,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="4">
         <v>2</v>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4">
         <v>2</v>
@@ -9134,10 +9134,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -9146,10 +9146,10 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" s="3">
         <f>IF(B24 = F24, 1, 0)</f>
@@ -9167,10 +9167,10 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -9179,10 +9179,10 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3">
         <f>IF(B25 = F25, 1, 0)</f>
@@ -9200,10 +9200,10 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -9212,10 +9212,10 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3">
         <f>IF(B26 = F26, 1, 0)</f>
@@ -9233,10 +9233,10 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -9245,10 +9245,10 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="3">
         <f>IF(B27 = F27, 1, 0)</f>
@@ -9266,10 +9266,10 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -9278,10 +9278,10 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3">
         <f>IF(B28 = F28, 1, 0)</f>
@@ -9299,10 +9299,10 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -9311,10 +9311,10 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="3">
         <f>IF(B29 = F29, 1, 0)</f>
@@ -9332,10 +9332,10 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3">
         <f>IF(B30 = F30, 1, 0)</f>
@@ -9365,10 +9365,10 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -9377,10 +9377,10 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3">
         <f>IF(B31 = F31, 1, 0)</f>
@@ -9398,10 +9398,10 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -9410,10 +9410,10 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="3">
         <f>IF(B32 = F32, 1, 0)</f>
@@ -9431,10 +9431,10 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -9443,10 +9443,10 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="3">
         <f>IF(B33 = F33, 1, 0)</f>
@@ -9464,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -9476,7 +9476,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
@@ -9497,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4">
         <v>0</v>
@@ -9530,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="4">
         <v>0</v>
@@ -10546,7 +10546,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -10567,25 +10567,25 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" s="3">
         <f>IF(B9 = I9, 1, 0)</f>
@@ -10601,7 +10601,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -10622,25 +10622,25 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" s="3">
         <f>IF(B10 = I10, 1, 0)</f>
@@ -10656,7 +10656,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -10677,25 +10677,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3">
         <f>IF(B11 = I11, 1, 0)</f>
@@ -10876,7 +10876,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -10897,25 +10897,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3">
         <f>IF(B15 = I15, 1, 0)</f>
@@ -10931,7 +10931,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -10952,25 +10952,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" s="3">
         <f>IF(B16 = I16, 1, 0)</f>
@@ -10986,7 +10986,7 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -11007,25 +11007,25 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P17" s="3">
         <f>IF(B17 = I17, 1, 0)</f>
@@ -11041,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -11053,7 +11053,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -11062,25 +11062,25 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" s="3">
         <f>IF(B18 = I18, 1, 0)</f>
@@ -11096,7 +11096,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -11117,25 +11117,25 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" s="3">
         <f>IF(B19 = I19, 1, 0)</f>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -11649,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -11670,7 +11670,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -11954,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -12260,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -12281,7 +12281,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -12315,7 +12315,7 @@
         <v>1</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -12336,7 +12336,7 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -12651,7 +12651,7 @@
         <v>1</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="4">
         <v>1</v>
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="4">
         <v>0</v>
@@ -12859,7 +12859,7 @@
         <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -12880,7 +12880,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -13562,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -13583,7 +13583,7 @@
         <v>2</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4">
         <v>2</v>
@@ -13932,7 +13932,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -13953,25 +13953,25 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O18" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P18" s="3">
         <f>IF(B18 = I18, 1, 0)</f>
@@ -14042,16 +14042,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -14063,25 +14063,25 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <f>IF(B20 = I20, 1, 0)</f>
@@ -14097,7 +14097,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -14118,25 +14118,25 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <f>IF(B21 = I21, 1, 0)</f>
@@ -14152,7 +14152,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -14173,25 +14173,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <f>IF(B22 = I22, 1, 0)</f>
@@ -14207,7 +14207,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -14228,25 +14228,25 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
         <f>IF(B23 = I23, 1, 0)</f>
@@ -14262,7 +14262,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -14283,25 +14283,25 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <f>IF(B24 = I24, 1, 0)</f>
@@ -14317,7 +14317,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -14338,25 +14338,25 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P25" s="3">
         <f>IF(B25 = I25, 1, 0)</f>
@@ -14372,13 +14372,13 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -14393,25 +14393,25 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>2</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P26" s="3">
         <f>IF(B26 = I26, 1, 0)</f>
@@ -14427,7 +14427,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -14448,25 +14448,25 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3">
         <f>IF(B27 = I27, 1, 0)</f>
@@ -14482,7 +14482,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -14503,25 +14503,25 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3">
         <f>IF(B28 = I28, 1, 0)</f>
@@ -14537,7 +14537,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -14558,25 +14558,25 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P29" s="3">
         <f>IF(B29 = I29, 1, 0)</f>
@@ -14592,7 +14592,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -14613,25 +14613,25 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3">
         <f>IF(B30 = I30, 1, 0)</f>
@@ -14647,7 +14647,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -14668,25 +14668,25 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3">
         <f>IF(B31 = I31, 1, 0)</f>
@@ -14702,7 +14702,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -14723,25 +14723,25 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <f>IF(B32 = I32, 1, 0)</f>
@@ -14757,7 +14757,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -14778,25 +14778,25 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3">
         <f>IF(B33 = I33, 1, 0)</f>
@@ -14812,7 +14812,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -14833,25 +14833,25 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
         <f>IF(B34 = I34, 1, 0)</f>
@@ -14867,7 +14867,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -14888,25 +14888,25 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3">
         <f>IF(B35 = I35, 1, 0)</f>
@@ -14922,7 +14922,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -14943,25 +14943,25 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3">
         <f>IF(B36 = I36, 1, 0)</f>
@@ -15145,7 +15145,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -15166,7 +15166,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -15585,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -15606,7 +15606,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -15958,7 +15958,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
@@ -15979,7 +15979,7 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" s="4">
         <v>2</v>
@@ -16181,7 +16181,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -16202,7 +16202,7 @@
         <v>2</v>
       </c>
       <c r="O6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3">
         <f>IF(B6 = I6, 1, 0)</f>
@@ -16273,7 +16273,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -16294,25 +16294,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="3">
         <f>IF(B8 = I8, 1, 0)</f>
@@ -16948,7 +16948,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4">
         <v>1</v>
@@ -16969,7 +16969,7 @@
         <v>2</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="4">
         <v>2</v>
@@ -17153,7 +17153,7 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -17174,25 +17174,25 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P24" s="3">
         <f>IF(B24 = I24, 1, 0)</f>
@@ -17208,7 +17208,7 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -17229,25 +17229,25 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" s="3">
         <f>IF(B25 = I25, 1, 0)</f>
@@ -17263,7 +17263,7 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -17284,25 +17284,25 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" s="3">
         <f>IF(B26 = I26, 1, 0)</f>
@@ -17318,7 +17318,7 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -17339,25 +17339,25 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" s="3">
         <f>IF(B27 = I27, 1, 0)</f>
@@ -17373,7 +17373,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -17394,25 +17394,25 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3">
         <f>IF(B28 = I28, 1, 0)</f>
@@ -17428,7 +17428,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -17449,25 +17449,25 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3">
         <f>IF(B29 = I29, 1, 0)</f>
@@ -17483,7 +17483,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -17504,25 +17504,25 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" s="3">
         <f>IF(B30 = I30, 1, 0)</f>
@@ -17538,7 +17538,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -17559,25 +17559,25 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" s="3">
         <f>IF(B31 = I31, 1, 0)</f>
@@ -17593,7 +17593,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -17614,25 +17614,25 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P32" s="3">
         <f>IF(B32 = I32, 1, 0)</f>
@@ -17648,7 +17648,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -17669,25 +17669,25 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" s="3">
         <f>IF(B33 = I33, 1, 0)</f>
@@ -17721,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -17742,7 +17742,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
         <f>IF(B34 = I34, 1, 0)</f>
@@ -18045,7 +18045,7 @@
         <v>1</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -18066,7 +18066,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -18314,7 +18314,7 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -18335,7 +18335,7 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -18534,7 +18534,7 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -18555,7 +18555,7 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -18705,7 +18705,7 @@
         <v>1</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -18726,7 +18726,7 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52">
         <v>0</v>
@@ -18846,28 +18846,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
         <f>IF(B3 = F3, 1, 0)</f>
@@ -18879,7 +18879,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -18888,10 +18888,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -18900,7 +18900,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3">
         <f>IF(B4 = F4, 1, 0)</f>
@@ -18912,7 +18912,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -18921,10 +18921,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -18933,7 +18933,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3">
         <f>IF(B5 = F5, 1, 0)</f>
@@ -18945,7 +18945,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -18954,10 +18954,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -18966,7 +18966,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
         <f>IF(B6 = F6, 1, 0)</f>
@@ -18978,7 +18978,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -18987,10 +18987,10 @@
         <v>2</v>
       </c>
       <c r="E7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -18999,7 +18999,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3">
         <f>IF(B7 = F7, 1, 0)</f>
@@ -19011,7 +19011,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -19020,10 +19020,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -19032,7 +19032,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <f>IF(B8 = F8, 1, 0)</f>
@@ -19053,10 +19053,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -19065,7 +19065,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3">
         <f>IF(B9 = F9, 1, 0)</f>
@@ -19086,10 +19086,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -19098,7 +19098,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <f>IF(B10 = F10, 1, 0)</f>
@@ -19116,22 +19116,22 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3">
         <f>IF(B11 = F11, 1, 0)</f>
@@ -19149,22 +19149,22 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3">
         <f>IF(B12 = F12, 1, 0)</f>
@@ -19185,10 +19185,10 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -19197,7 +19197,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3">
         <f>IF(B13 = F13, 1, 0)</f>
@@ -19218,10 +19218,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -19230,7 +19230,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <f>IF(B14 = F14, 1, 0)</f>
@@ -19251,10 +19251,10 @@
         <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -19263,7 +19263,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <f>IF(B15 = F15, 1, 0)</f>
@@ -19284,10 +19284,10 @@
         <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -19296,7 +19296,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3">
         <f>IF(B16 = F16, 1, 0)</f>
@@ -19380,7 +19380,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -19392,7 +19392,7 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -19446,7 +19446,7 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -19458,7 +19458,7 @@
         <v>2</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -19476,10 +19476,10 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -19488,10 +19488,10 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -19512,7 +19512,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -19524,7 +19524,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -19578,7 +19578,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -19590,7 +19590,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -19677,7 +19677,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -19689,7 +19689,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="4">
         <v>0</v>
@@ -19710,7 +19710,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -19722,7 +19722,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4">
         <v>0</v>
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -19755,7 +19755,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="4">
         <v>0</v>
@@ -19776,7 +19776,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
@@ -19788,7 +19788,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4">
         <v>0</v>
@@ -19809,7 +19809,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
@@ -19821,7 +19821,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="4">
         <v>0</v>
@@ -19842,7 +19842,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -19854,7 +19854,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="4">
         <v>0</v>
@@ -19875,7 +19875,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -19887,7 +19887,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
@@ -19908,7 +19908,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -19920,7 +19920,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="4">
         <v>0</v>
@@ -19941,7 +19941,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="4">
         <v>0</v>
@@ -19974,7 +19974,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -19986,7 +19986,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="4">
         <v>0</v>
@@ -20007,7 +20007,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
@@ -20019,7 +20019,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" s="4">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -20052,7 +20052,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" s="4">
         <v>0</v>
@@ -20073,7 +20073,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -20085,7 +20085,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4">
         <v>0</v>
@@ -20106,7 +20106,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="4">
         <v>0</v>
@@ -20139,7 +20139,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -20151,7 +20151,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" s="4">
         <v>0</v>
@@ -20172,7 +20172,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -20184,7 +20184,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I43" s="4">
         <v>0</v>
@@ -20205,7 +20205,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4">
         <v>0</v>
@@ -20238,7 +20238,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -20250,7 +20250,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4">
         <v>0</v>
@@ -20271,7 +20271,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -20283,7 +20283,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" s="4">
         <v>0</v>
@@ -20304,7 +20304,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
@@ -20316,7 +20316,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="4">
         <v>0</v>
@@ -20337,7 +20337,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -20349,7 +20349,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="4">
         <v>0</v>
@@ -20370,7 +20370,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -20382,7 +20382,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="4">
         <v>0</v>
@@ -20403,7 +20403,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -20415,7 +20415,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="4">
         <v>0</v>
@@ -20436,7 +20436,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -20448,7 +20448,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="4">
         <v>0</v>
@@ -20469,7 +20469,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -20481,7 +20481,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52" s="4">
         <v>0</v>
@@ -20627,7 +20627,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -20648,25 +20648,25 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" s="3">
         <f>IF(B3 = I3, 1, 0)</f>
@@ -20960,7 +20960,7 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -20981,7 +20981,7 @@
         <v>2</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -21635,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -21656,7 +21656,7 @@
         <v>2</v>
       </c>
       <c r="O21" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="3">
         <f>IF(B21 = I21, 1, 0)</f>
@@ -21672,7 +21672,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -21693,25 +21693,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P22" s="3">
         <f>IF(B22 = I22, 1, 0)</f>
@@ -22350,7 +22350,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -22371,7 +22371,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="3">
         <f>IF(B34 = I34, 1, 0)</f>
@@ -22396,7 +22396,7 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -22417,7 +22417,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -22564,7 +22564,7 @@
         <v>1</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -22585,7 +22585,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -22720,7 +22720,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -22741,7 +22741,7 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -23053,7 +23053,7 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -23074,7 +23074,7 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -23270,7 +23270,7 @@
         <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -23291,7 +23291,7 @@
         <v>0</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -23860,7 +23860,7 @@
         <v>1</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -23881,7 +23881,7 @@
         <v>2</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N9">
         <v>2</v>
@@ -23958,7 +23958,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -23979,25 +23979,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="3">
         <f>IF(B11 = I11, 1, 0)</f>
@@ -24013,7 +24013,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -24034,25 +24034,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="3">
         <f>IF(B12 = I12, 1, 0)</f>
@@ -24083,7 +24083,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="4">
         <v>1</v>
@@ -24104,7 +24104,7 @@
         <v>2</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4">
         <v>2</v>
@@ -24196,7 +24196,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -24217,7 +24217,7 @@
         <v>2</v>
       </c>
       <c r="O15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3">
         <f>IF(B15 = I15, 1, 0)</f>
@@ -24398,7 +24398,7 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -24419,25 +24419,25 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" s="3">
         <f>IF(B19 = I19, 1, 0)</f>
@@ -24508,7 +24508,7 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -24529,25 +24529,25 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21" s="3">
         <f>IF(B21 = I21, 1, 0)</f>
@@ -24563,7 +24563,7 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -24584,25 +24584,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" s="3">
         <f>IF(B22 = I22, 1, 0)</f>
@@ -24618,7 +24618,7 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -24639,25 +24639,25 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="3">
         <f>IF(B23 = I23, 1, 0)</f>
@@ -24728,10 +24728,10 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -24749,25 +24749,25 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P25" s="3">
         <f>IF(B25 = I25, 1, 0)</f>
@@ -24795,7 +24795,7 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -24816,7 +24816,7 @@
         <v>2</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>2</v>
@@ -24893,7 +24893,7 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -24905,7 +24905,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -24914,25 +24914,25 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P28" s="3">
         <f>IF(B28 = I28, 1, 0)</f>
@@ -24948,7 +24948,7 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -24969,25 +24969,25 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29" s="3">
         <f>IF(B29 = I29, 1, 0)</f>
@@ -25003,7 +25003,7 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -25024,25 +25024,25 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P30" s="3">
         <f>IF(B30 = I30, 1, 0)</f>
@@ -25058,7 +25058,7 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -25079,25 +25079,25 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31" s="3">
         <f>IF(B31 = I31, 1, 0)</f>
@@ -25113,7 +25113,7 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -25134,25 +25134,25 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32" s="3">
         <f>IF(B32 = I32, 1, 0)</f>
@@ -25168,7 +25168,7 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -25189,25 +25189,25 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" s="3">
         <f>IF(B33 = I33, 1, 0)</f>
@@ -25223,7 +25223,7 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -25244,25 +25244,25 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" s="3">
         <f>IF(B34 = I34, 1, 0)</f>
@@ -25278,7 +25278,7 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -25299,25 +25299,25 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" s="3">
         <f>IF(B35 = I35, 1, 0)</f>
@@ -25333,7 +25333,7 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -25345,7 +25345,7 @@
         <v>1</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -25354,25 +25354,25 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36">
         <v>2</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P36" s="3">
         <f>IF(B36 = I36, 1, 0)</f>
@@ -25388,7 +25388,7 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -25409,25 +25409,25 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P37" s="3">
         <f>IF(B37 = I37, 1, 0)</f>
@@ -25443,7 +25443,7 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -25464,25 +25464,25 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P38" s="3">
         <f>IF(B38 = I38, 1, 0)</f>
@@ -25498,7 +25498,7 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -25519,25 +25519,25 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" s="3">
         <f>IF(B39 = I39, 1, 0)</f>
@@ -25553,7 +25553,7 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -25574,25 +25574,25 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" s="3">
         <f>IF(B40 = I40, 1, 0)</f>
@@ -25608,7 +25608,7 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -25629,25 +25629,25 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" s="3">
         <f>IF(B41 = I41, 1, 0)</f>
@@ -25663,7 +25663,7 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -25684,25 +25684,25 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O42" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P42" s="3">
         <f>IF(B42 = I42, 1, 0)</f>
@@ -25718,7 +25718,7 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -25739,25 +25739,25 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P43" s="3">
         <f>IF(B43 = I43, 1, 0)</f>
@@ -25773,7 +25773,7 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -25794,25 +25794,25 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P44" s="3">
         <f>IF(B44 = I44, 1, 0)</f>
@@ -25828,7 +25828,7 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -25849,25 +25849,25 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="3">
         <f>IF(B45 = I45, 1, 0)</f>
@@ -25883,7 +25883,7 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -25904,25 +25904,25 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="3">
         <f>IF(B46 = I46, 1, 0)</f>
@@ -25938,7 +25938,7 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -25959,25 +25959,25 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" s="3">
         <f>IF(B47 = I47, 1, 0)</f>
@@ -25993,7 +25993,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -26014,25 +26014,25 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="3">
         <f>IF(B48 = I48, 1, 0)</f>
@@ -26048,7 +26048,7 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -26069,25 +26069,25 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="3">
         <f>IF(B49 = I49, 1, 0)</f>
@@ -26103,7 +26103,7 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -26118,31 +26118,31 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="4">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="3">
         <f>IF(B50 = I50, 1, 0)</f>
@@ -26158,7 +26158,7 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -26179,25 +26179,25 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51" s="3">
         <f>IF(B51 = I51, 1, 0)</f>
@@ -26213,7 +26213,7 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -26234,25 +26234,25 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P52" s="3">
         <f>IF(B52 = I52, 1, 0)</f>
@@ -26369,7 +26369,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="4">
         <v>1</v>
@@ -26390,7 +26390,7 @@
         <v>2</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" s="4">
         <v>2</v>
@@ -26409,7 +26409,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -26430,25 +26430,25 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
         <f>IF(B3 = I3, 1, 0)</f>
@@ -26464,7 +26464,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -26485,25 +26485,25 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3">
         <f>IF(B4 = I4, 1, 0)</f>
@@ -26519,7 +26519,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -26540,25 +26540,25 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3">
         <f>IF(B5 = I5, 1, 0)</f>
@@ -26574,7 +26574,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -26592,25 +26592,25 @@
         <v>1</v>
       </c>
       <c r="H6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" s="4">
         <v>0</v>
@@ -26629,10 +26629,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -26650,25 +26650,25 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" s="3">
         <f>IF(B7 = I7, 1, 0)</f>
@@ -26684,7 +26684,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -26705,25 +26705,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <f>IF(B8 = I8, 1, 0)</f>
@@ -26739,7 +26739,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -26760,25 +26760,25 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <f>IF(B9 = I9, 1, 0)</f>
@@ -26794,7 +26794,7 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -26815,25 +26815,25 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
         <f>IF(B10 = I10, 1, 0)</f>
@@ -26849,7 +26849,7 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -26870,25 +26870,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" s="3">
         <f>IF(B11 = I11, 1, 0)</f>
@@ -26904,7 +26904,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -26925,25 +26925,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3">
         <f>IF(B12 = I12, 1, 0)</f>
@@ -26959,10 +26959,10 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -26980,25 +26980,25 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O13" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" s="3">
         <f>IF(B13 = I13, 1, 0)</f>
@@ -27014,7 +27014,7 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -27026,34 +27026,34 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="4">
         <v>1</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14">
         <v>0</v>
       </c>
       <c r="O14" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
         <f>IF(B14 = I14, 1, 0)</f>
@@ -27069,7 +27069,7 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -27090,25 +27090,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
         <f>IF(B15 = I15, 1, 0)</f>
@@ -27124,7 +27124,7 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -27145,25 +27145,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P16" s="3">
         <f>IF(B16 = I16, 1, 0)</f>
@@ -27188,7 +27188,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -27209,7 +27209,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -27273,7 +27273,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P18" s="3">
         <f>IF(B18 = I18, 1, 0)</f>
@@ -27356,7 +27356,7 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -27377,7 +27377,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -27402,7 +27402,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -27417,13 +27417,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -27438,7 +27438,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" s="3">
         <f>IF(B21 = I21, 1, 0)</f>
@@ -28233,13 +28233,13 @@
         <v>1</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="4">
         <v>1</v>
@@ -28254,13 +28254,13 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36">
         <v>0</v>
       </c>
       <c r="N36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="4">
         <v>0</v>
@@ -28288,7 +28288,7 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -28309,7 +28309,7 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -28453,7 +28453,7 @@
         <v>1</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -28474,7 +28474,7 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -28612,7 +28612,7 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -28633,7 +28633,7 @@
         <v>0</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -28780,13 +28780,13 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -28801,13 +28801,13 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -28954,7 +28954,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="4">
         <v>1</v>
@@ -28975,7 +28975,7 @@
         <v>0</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="4">
         <v>0</v>

--- a/shipClassTests/testResults/sensed_system_with_subsystems_test.xlsx
+++ b/shipClassTests/testResults/sensed_system_with_subsystems_test.xlsx
@@ -515,7 +515,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
         <f>IF(B2 = E2, 1, 0)</f>
@@ -533,16 +533,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3">
         <f>IF(B3 = E3, 1, 0)</f>
@@ -554,13 +554,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -569,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3">
         <f>IF(B4 = E4, 1, 0)</f>
@@ -581,22 +581,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
         <f>IF(B5 = E5, 1, 0)</f>
@@ -608,22 +608,22 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <f>IF(B6 = E6, 1, 0)</f>
@@ -635,22 +635,22 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="3">
         <f>IF(B7 = E7, 1, 0)</f>
@@ -662,10 +662,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4">
         <v>0</v>
@@ -689,19 +689,19 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="4">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -716,22 +716,22 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3">
         <f>IF(B10 = E10, 1, 0)</f>
@@ -743,19 +743,19 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
@@ -770,10 +770,10 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3">
         <f>IF(B13 = E13, 1, 0)</f>
@@ -833,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3">
         <f>IF(B14 = E14, 1, 0)</f>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
@@ -914,13 +914,13 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="3">
         <f>IF(B17 = E17, 1, 0)</f>
@@ -995,13 +995,13 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="3">
         <f>IF(B20 = E20, 1, 0)</f>
@@ -1076,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3">
         <f>IF(B23 = E23, 1, 0)</f>
@@ -1157,13 +1157,13 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="3">
         <f>IF(B26 = E26, 1, 0)</f>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3">
         <f>IF(B29 = E29, 1, 0)</f>
@@ -1292,10 +1292,10 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4">
         <v>0</v>
@@ -1319,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -1481,10 +1481,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="4">
         <v>0</v>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="4">
         <v>0</v>
@@ -1697,10 +1697,10 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="4">
         <v>0</v>
@@ -1859,13 +1859,13 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
       <c r="G52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3">
         <f>IF(B52 = E52, 1, 0)</f>
@@ -1997,13 +1997,13 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4">
         <v>2</v>
@@ -2018,13 +2018,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4">
         <v>2</v>
@@ -2051,19 +2051,19 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -2072,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3">
         <f>IF(B5 = F5, 1, 0)</f>
@@ -2084,16 +2084,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3">
         <f>IF(B6 = F6, 1, 0)</f>
@@ -2117,7 +2117,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -2126,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>2</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2192,19 +2192,19 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>2</v>
       </c>
       <c r="I9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="3">
         <f>IF(B9 = F9, 1, 0)</f>
@@ -2216,28 +2216,28 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3">
         <f>IF(B10 = F10, 1, 0)</f>
@@ -2249,28 +2249,28 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3">
         <f>IF(B11 = F11, 1, 0)</f>
@@ -2282,7 +2282,7 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2291,19 +2291,19 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
         <f>IF(B12 = F12, 1, 0)</f>
@@ -2321,22 +2321,22 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f>IF(B13 = F13, 1, 0)</f>
@@ -2351,25 +2351,25 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3">
         <f>IF(B14 = F14, 1, 0)</f>
@@ -2384,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -2417,25 +2417,25 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>2</v>
       </c>
       <c r="I16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3">
         <f>IF(B16 = F16, 1, 0)</f>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2465,10 +2465,10 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3">
         <f>IF(B17 = F17, 1, 0)</f>
@@ -2483,10 +2483,10 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3">
         <f>IF(B18 = F18, 1, 0)</f>
@@ -2519,7 +2519,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4">
         <v>0</v>
@@ -2528,10 +2528,10 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -2552,7 +2552,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3">
         <f>IF(B20 = F20, 1, 0)</f>
@@ -2585,7 +2585,7 @@
         <v>2</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -2651,7 +2651,7 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
         <v>0</v>
@@ -2660,13 +2660,13 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3">
         <f>IF(B23 = F23, 1, 0)</f>
@@ -2681,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -2696,7 +2696,7 @@
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
         <v>0</v>
@@ -2726,13 +2726,13 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3">
         <f>IF(B25 = F25, 1, 0)</f>
@@ -2750,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -2762,10 +2762,10 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3">
         <f>IF(B26 = F26, 1, 0)</f>
@@ -2783,7 +2783,7 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="3">
         <f>IF(B27 = F27, 1, 0)</f>
@@ -2816,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4">
         <v>0</v>
@@ -2828,10 +2828,10 @@
         <v>2</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3">
         <f>IF(B28 = F28, 1, 0)</f>
@@ -2849,7 +2849,7 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>2</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
         <v>0</v>
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="3">
         <f>IF(B30 = F30, 1, 0)</f>
@@ -2912,16 +2912,16 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -2930,7 +2930,7 @@
         <v>2</v>
       </c>
       <c r="I31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="3">
         <f>IF(B31 = F31, 1, 0)</f>
@@ -2948,22 +2948,22 @@
         <v>2</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="4">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>2</v>
       </c>
       <c r="I32" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="3">
         <f>IF(B32 = F32, 1, 0)</f>
@@ -2981,7 +2981,7 @@
         <v>2</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
         <v>0</v>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="3">
         <f>IF(B33 = F33, 1, 0)</f>
@@ -3014,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
         <v>0</v>
@@ -3023,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4">
         <v>0</v>
@@ -3056,13 +3056,13 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="3">
         <f>IF(B35 = F35, 1, 0)</f>
@@ -3077,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="4">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4">
         <v>0</v>
@@ -3122,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="3">
         <f>IF(B37 = F37, 1, 0)</f>
@@ -3143,25 +3143,25 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="3">
         <f>IF(B38 = F38, 1, 0)</f>
@@ -3176,10 +3176,10 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="4">
         <v>0</v>
@@ -3188,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>2</v>
       </c>
       <c r="I39" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="3">
         <f>IF(B39 = F39, 1, 0)</f>
@@ -3209,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>2</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" s="4">
         <v>0</v>
@@ -3245,22 +3245,22 @@
         <v>2</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>2</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="3">
         <f>IF(B41 = F41, 1, 0)</f>
@@ -3278,7 +3278,7 @@
         <v>2</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>2</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="4">
         <v>0</v>
@@ -3323,7 +3323,7 @@
         <v>2</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I43" s="4">
         <v>0</v>
@@ -3344,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4">
         <v>0</v>
@@ -3353,13 +3353,13 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" s="3">
         <f>IF(B44 = F44, 1, 0)</f>
@@ -3377,7 +3377,7 @@
         <v>2</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" s="4">
         <v>0</v>
@@ -3410,13 +3410,13 @@
         <v>2</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3425,7 +3425,7 @@
         <v>2</v>
       </c>
       <c r="I46" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="3">
         <f>IF(B46 = F46, 1, 0)</f>
@@ -3443,22 +3443,22 @@
         <v>2</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E47" s="4">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" s="3">
         <f>IF(B47 = F47, 1, 0)</f>
@@ -3476,7 +3476,7 @@
         <v>2</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>2</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="4">
         <v>0</v>
@@ -3521,10 +3521,10 @@
         <v>2</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="3">
         <f>IF(B49 = F49, 1, 0)</f>
@@ -3542,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4">
         <v>0</v>
@@ -3554,7 +3554,7 @@
         <v>2</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="4">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>2</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4">
         <v>0</v>
@@ -3584,13 +3584,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="3">
         <f>IF(B51 = F51, 1, 0)</f>
@@ -3608,7 +3608,7 @@
         <v>2</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="4">
         <v>0</v>
@@ -3709,13 +3709,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3 = D3, 1, 0)</f>
@@ -3859,13 +3859,13 @@
         <v>2</v>
       </c>
       <c r="C9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9 = D9, 1, 0)</f>
@@ -3881,16 +3881,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <f>IF(B10 = D10, 1, 0)</f>
@@ -3909,13 +3909,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -3934,13 +3934,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12 = D12, 1, 0)</f>
@@ -3959,13 +3959,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13 = D13, 1, 0)</f>
@@ -3981,16 +3981,16 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -4006,16 +4006,16 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15 = D15, 1, 0)</f>
@@ -4031,16 +4031,16 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16 = D16, 1, 0)</f>
@@ -4056,10 +4056,10 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4081,16 +4081,16 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18 = D18, 1, 0)</f>
@@ -4109,13 +4109,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
         <f>IF(B19 = D19, 1, 0)</f>
@@ -4134,13 +4134,13 @@
         <v>2</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -4184,13 +4184,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <f>IF(B22 = D22, 1, 0)</f>
@@ -4209,13 +4209,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23 = D23, 1, 0)</f>
@@ -4231,10 +4231,10 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -4256,16 +4256,16 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25 = D25, 1, 0)</f>
@@ -4309,13 +4309,13 @@
         <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3">
         <f>IF(B27 = D27, 1, 0)</f>
@@ -4381,16 +4381,16 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3">
         <f>IF(B30 = D30, 1, 0)</f>
@@ -4406,10 +4406,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -4434,13 +4434,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32 = D32, 1, 0)</f>
@@ -4459,13 +4459,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
         <f>IF(B33 = D33, 1, 0)</f>
@@ -4484,13 +4484,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34 = D34, 1, 0)</f>
@@ -4506,16 +4506,16 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
         <f>IF(B35 = D35, 1, 0)</f>
@@ -4531,16 +4531,16 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36 = D36, 1, 0)</f>
@@ -4559,13 +4559,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3">
         <f>IF(B37 = D37, 1, 0)</f>
@@ -4581,16 +4581,16 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38 = D38, 1, 0)</f>
@@ -4606,16 +4606,16 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39 = D39, 1, 0)</f>
@@ -4631,10 +4631,10 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -4734,13 +4734,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <f>IF(B44 = D44, 1, 0)</f>
@@ -4759,13 +4759,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45 = D45, 1, 0)</f>
@@ -4809,13 +4809,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47 = D47, 1, 0)</f>
@@ -4909,13 +4909,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51 = D51, 1, 0)</f>
@@ -5040,13 +5040,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3 = D3, 1, 0)</f>
@@ -5062,10 +5062,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -5087,10 +5087,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -5112,16 +5112,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3">
         <f>IF(B6 = D6, 1, 0)</f>
@@ -5165,13 +5165,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8 = D8, 1, 0)</f>
@@ -5212,16 +5212,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="3">
         <f>IF(B10 = D10, 1, 0)</f>
@@ -5237,16 +5237,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -5265,13 +5265,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12 = D12, 1, 0)</f>
@@ -5287,16 +5287,16 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13 = D13, 1, 0)</f>
@@ -5312,16 +5312,16 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -5337,16 +5337,16 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15 = D15, 1, 0)</f>
@@ -5362,10 +5362,10 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -5387,16 +5387,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4">
         <v>1</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17 = D17, 1, 0)</f>
@@ -5412,16 +5412,16 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18 = D18, 1, 0)</f>
@@ -5437,16 +5437,16 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
         <f>IF(B19 = D19, 1, 0)</f>
@@ -5462,16 +5462,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -5487,16 +5487,16 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" s="4">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3">
         <f>IF(B21 = D21, 1, 0)</f>
@@ -5512,10 +5512,10 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -5537,16 +5537,16 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23 = D23, 1, 0)</f>
@@ -5562,16 +5562,16 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
         <f>IF(B24 = D24, 1, 0)</f>
@@ -5587,16 +5587,16 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25 = D25, 1, 0)</f>
@@ -5612,16 +5612,16 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26 = D26, 1, 0)</f>
@@ -5637,10 +5637,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -5662,16 +5662,16 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28 = D28, 1, 0)</f>
@@ -5687,16 +5687,16 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <f>IF(B29 = D29, 1, 0)</f>
@@ -5712,16 +5712,16 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="3">
         <f>IF(B30 = D30, 1, 0)</f>
@@ -5737,10 +5737,10 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -5762,10 +5762,10 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -5787,16 +5787,16 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="3">
         <f>IF(B33 = D33, 1, 0)</f>
@@ -5812,16 +5812,16 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34 = D34, 1, 0)</f>
@@ -5837,16 +5837,16 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C35" s="4">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3">
         <f>IF(B35 = D35, 1, 0)</f>
@@ -5862,16 +5862,16 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36 = D36, 1, 0)</f>
@@ -5887,10 +5887,10 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C37" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -5912,16 +5912,16 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38 = D38, 1, 0)</f>
@@ -5937,10 +5937,10 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C39" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -5962,16 +5962,16 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C40" s="4">
         <v>1</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40 = D40, 1, 0)</f>
@@ -5987,16 +5987,16 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41 = D41, 1, 0)</f>
@@ -6012,10 +6012,10 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -6037,16 +6037,16 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C43" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43 = D43, 1, 0)</f>
@@ -6062,16 +6062,16 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
         <f>IF(B44 = D44, 1, 0)</f>
@@ -6087,16 +6087,16 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45 = D45, 1, 0)</f>
@@ -6112,10 +6112,10 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -6137,16 +6137,16 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47 = D47, 1, 0)</f>
@@ -6162,10 +6162,10 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -6187,16 +6187,16 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49 = D49, 1, 0)</f>
@@ -6212,16 +6212,16 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C50" s="4">
         <v>1</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3">
         <f>IF(B50 = D50, 1, 0)</f>
@@ -6237,16 +6237,16 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51 = D51, 1, 0)</f>
@@ -6262,16 +6262,16 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="4">
         <v>1</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52 = D52, 1, 0)</f>
@@ -6418,16 +6418,16 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3">
         <f>IF(B5 = D5, 1, 0)</f>
@@ -6443,16 +6443,16 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3">
         <f>IF(B6 = D6, 1, 0)</f>
@@ -6468,10 +6468,10 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6493,10 +6493,10 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6518,16 +6518,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9 = D9, 1, 0)</f>
@@ -6543,16 +6543,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
         <f>IF(B10 = D10, 1, 0)</f>
@@ -6568,16 +6568,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -6593,16 +6593,16 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12 = D12, 1, 0)</f>
@@ -6618,16 +6618,16 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13 = D13, 1, 0)</f>
@@ -6643,16 +6643,16 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -6668,10 +6668,10 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6693,16 +6693,16 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16 = D16, 1, 0)</f>
@@ -6718,16 +6718,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17 = D17, 1, 0)</f>
@@ -6746,13 +6746,13 @@
         <v>0</v>
       </c>
       <c r="C18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18 = D18, 1, 0)</f>
@@ -6796,13 +6796,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -6871,13 +6871,13 @@
         <v>0</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23 = D23, 1, 0)</f>
@@ -6921,13 +6921,13 @@
         <v>0</v>
       </c>
       <c r="C25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25 = D25, 1, 0)</f>
@@ -6946,13 +6946,13 @@
         <v>0</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26 = D26, 1, 0)</f>
@@ -6971,13 +6971,13 @@
         <v>0</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="3">
         <f>IF(B27 = D27, 1, 0)</f>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28 = D28, 1, 0)</f>
@@ -7046,13 +7046,13 @@
         <v>0</v>
       </c>
       <c r="C30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3">
         <f>IF(B30 = D30, 1, 0)</f>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="C31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
         <f>IF(B31 = D31, 1, 0)</f>
@@ -7096,13 +7096,13 @@
         <v>0</v>
       </c>
       <c r="C32" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32 = D32, 1, 0)</f>
@@ -7121,13 +7121,13 @@
         <v>0</v>
       </c>
       <c r="C33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
         <f>IF(B33 = D33, 1, 0)</f>
@@ -7171,13 +7171,13 @@
         <v>0</v>
       </c>
       <c r="C35" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="3">
         <f>IF(B35 = D35, 1, 0)</f>
@@ -7221,13 +7221,13 @@
         <v>0</v>
       </c>
       <c r="C37" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3">
         <f>IF(B37 = D37, 1, 0)</f>
@@ -7246,13 +7246,13 @@
         <v>0</v>
       </c>
       <c r="C38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38 = D38, 1, 0)</f>
@@ -7271,13 +7271,13 @@
         <v>0</v>
       </c>
       <c r="C39" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="3">
         <f>IF(B39 = D39, 1, 0)</f>
@@ -7321,13 +7321,13 @@
         <v>0</v>
       </c>
       <c r="C41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41 = D41, 1, 0)</f>
@@ -7396,13 +7396,13 @@
         <v>0</v>
       </c>
       <c r="C44" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3">
         <f>IF(B44 = D44, 1, 0)</f>
@@ -7446,13 +7446,13 @@
         <v>0</v>
       </c>
       <c r="C46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="3">
         <f>IF(B46 = D46, 1, 0)</f>
@@ -7471,13 +7471,13 @@
         <v>0</v>
       </c>
       <c r="C47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47 = D47, 1, 0)</f>
@@ -7521,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="C49" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49 = D49, 1, 0)</f>
@@ -7571,13 +7571,13 @@
         <v>0</v>
       </c>
       <c r="C51" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51 = D51, 1, 0)</f>
@@ -7695,16 +7695,16 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3">
         <f>IF(B2 = F2, 1, 0)</f>
@@ -7716,28 +7716,28 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>2</v>
       </c>
       <c r="I3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3">
         <f>IF(B3 = F3, 1, 0)</f>
@@ -7749,25 +7749,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4">
         <v>2</v>
@@ -7782,22 +7782,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4">
         <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -7815,19 +7815,19 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -7836,7 +7836,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3">
         <f>IF(B6 = F6, 1, 0)</f>
@@ -7854,22 +7854,22 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="3">
         <f>IF(B7 = F7, 1, 0)</f>
@@ -7887,22 +7887,22 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3">
         <f>IF(B8 = F8, 1, 0)</f>
@@ -7920,10 +7920,10 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>2</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3">
         <f>IF(B9 = F9, 1, 0)</f>
@@ -7953,13 +7953,13 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -7968,7 +7968,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3">
         <f>IF(B10 = F10, 1, 0)</f>
@@ -7989,19 +7989,19 @@
         <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" s="3">
         <f>IF(B11 = F11, 1, 0)</f>
@@ -8022,19 +8022,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3">
         <f>IF(B12 = F12, 1, 0)</f>
@@ -8055,19 +8055,19 @@
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f>IF(B13 = F13, 1, 0)</f>
@@ -8088,19 +8088,19 @@
         <v>0</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3">
         <f>IF(B14 = F14, 1, 0)</f>
@@ -8121,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="3">
         <f>IF(B15 = F15, 1, 0)</f>
@@ -8154,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="3">
         <f>IF(B16 = F16, 1, 0)</f>
@@ -8187,19 +8187,19 @@
         <v>0</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3">
         <f>IF(B17 = F17, 1, 0)</f>
@@ -8220,19 +8220,19 @@
         <v>0</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3">
         <f>IF(B18 = F18, 1, 0)</f>
@@ -8253,19 +8253,19 @@
         <v>0</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="3">
         <f>IF(B19 = F19, 1, 0)</f>
@@ -8280,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -8289,16 +8289,16 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="3">
         <f>IF(B20 = F20, 1, 0)</f>
@@ -8325,13 +8325,13 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3">
         <f>IF(B21 = F21, 1, 0)</f>
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3">
         <f>IF(B22 = F22, 1, 0)</f>
@@ -8388,16 +8388,16 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="3">
         <f>IF(B23 = F23, 1, 0)</f>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -8424,13 +8424,13 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="3">
         <f>IF(B24 = F24, 1, 0)</f>
@@ -8445,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -8457,13 +8457,13 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3">
         <f>IF(B25 = F25, 1, 0)</f>
@@ -8478,7 +8478,7 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -8487,16 +8487,16 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3">
         <f>IF(B26 = F26, 1, 0)</f>
@@ -8511,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -8544,7 +8544,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="4">
         <v>0</v>
@@ -8577,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -8586,16 +8586,16 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="3">
         <f>IF(B29 = F29, 1, 0)</f>
@@ -8610,7 +8610,7 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="4">
         <v>0</v>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -8655,13 +8655,13 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3">
         <f>IF(B31 = F31, 1, 0)</f>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -8709,7 +8709,7 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -8754,10 +8754,10 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="4">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -8787,7 +8787,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -8820,13 +8820,13 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="3">
         <f>IF(B36 = F36, 1, 0)</f>
@@ -8841,7 +8841,7 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -8853,7 +8853,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -8874,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -8886,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -8940,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -8952,13 +8952,13 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3">
         <f>IF(B40 = F40, 1, 0)</f>
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -8985,10 +8985,10 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="4">
         <v>0</v>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -9018,10 +9018,10 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4">
         <v>0</v>
@@ -9039,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -9051,13 +9051,13 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" s="3">
         <f>IF(B43 = F43, 1, 0)</f>
@@ -9072,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -9117,13 +9117,13 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" s="3">
         <f>IF(B45 = F45, 1, 0)</f>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46" s="4">
         <v>0</v>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -9186,7 +9186,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="4">
         <v>0</v>
@@ -9204,7 +9204,7 @@
         <v>0</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="3">
         <f>IF(B48 = F48, 1, 0)</f>
@@ -9237,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -9270,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -9282,10 +9282,10 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="4">
         <v>0</v>
@@ -9303,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -9315,13 +9315,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51" s="3">
         <f>IF(B51 = F51, 1, 0)</f>
@@ -9336,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -9345,16 +9345,16 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="3">
         <f>IF(B52 = F52, 1, 0)</f>
@@ -9415,13 +9415,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2 = D2, 1, 0)</f>
@@ -9440,13 +9440,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3 = D3, 1, 0)</f>
@@ -9490,13 +9490,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3">
         <f>IF(B5 = D5, 1, 0)</f>
@@ -9565,13 +9565,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8 = D8, 1, 0)</f>
@@ -9640,13 +9640,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -9665,13 +9665,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12 = D12, 1, 0)</f>
@@ -9715,13 +9715,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -9765,13 +9765,13 @@
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16 = D16, 1, 0)</f>
@@ -9815,13 +9815,13 @@
         <v>2</v>
       </c>
       <c r="C18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18 = D18, 1, 0)</f>
@@ -9840,13 +9840,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
         <f>IF(B19 = D19, 1, 0)</f>
@@ -9862,16 +9862,16 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -9890,13 +9890,13 @@
         <v>2</v>
       </c>
       <c r="C21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <f>IF(B21 = D21, 1, 0)</f>
@@ -9962,16 +9962,16 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
         <f>IF(B24 = D24, 1, 0)</f>
@@ -9987,16 +9987,16 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25 = D25, 1, 0)</f>
@@ -10012,16 +10012,16 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26 = D26, 1, 0)</f>
@@ -10037,10 +10037,10 @@
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -10062,10 +10062,10 @@
         <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -10087,16 +10087,16 @@
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3">
         <f>IF(B29 = D29, 1, 0)</f>
@@ -10112,16 +10112,16 @@
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="3">
         <f>IF(B30 = D30, 1, 0)</f>
@@ -10137,16 +10137,16 @@
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3">
         <f>IF(B31 = D31, 1, 0)</f>
@@ -10162,16 +10162,16 @@
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="4">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="3">
         <f>IF(B32 = D32, 1, 0)</f>
@@ -10187,16 +10187,16 @@
         <v>31</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" s="3">
         <f>IF(B33 = D33, 1, 0)</f>
@@ -10212,16 +10212,16 @@
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34 = D34, 1, 0)</f>
@@ -10237,16 +10237,16 @@
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C35" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="3">
         <f>IF(B35 = D35, 1, 0)</f>
@@ -10262,16 +10262,16 @@
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36 = D36, 1, 0)</f>
@@ -10287,16 +10287,16 @@
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37" s="4">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3">
         <f>IF(B37 = D37, 1, 0)</f>
@@ -10312,16 +10312,16 @@
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38 = D38, 1, 0)</f>
@@ -10337,10 +10337,10 @@
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -10362,16 +10362,16 @@
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" s="4">
         <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40 = D40, 1, 0)</f>
@@ -10387,16 +10387,16 @@
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41 = D41, 1, 0)</f>
@@ -10412,16 +10412,16 @@
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="3">
         <f>IF(B42 = D42, 1, 0)</f>
@@ -10437,16 +10437,16 @@
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" s="4">
         <v>1</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43 = D43, 1, 0)</f>
@@ -10462,10 +10462,10 @@
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C44" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -10487,16 +10487,16 @@
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45 = D45, 1, 0)</f>
@@ -10512,16 +10512,16 @@
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="3">
         <f>IF(B46 = D46, 1, 0)</f>
@@ -10537,10 +10537,10 @@
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -10562,10 +10562,10 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -10587,16 +10587,16 @@
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="3">
         <f>IF(B49 = D49, 1, 0)</f>
@@ -10612,16 +10612,16 @@
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C50" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3">
         <f>IF(B50 = D50, 1, 0)</f>
@@ -10637,16 +10637,16 @@
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51 = D51, 1, 0)</f>
@@ -10662,16 +10662,16 @@
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52 = D52, 1, 0)</f>
@@ -10768,10 +10768,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -10793,16 +10793,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3">
         <f>IF(B4 = D4, 1, 0)</f>
@@ -10818,7 +10818,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
@@ -10843,10 +10843,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -10868,16 +10868,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3">
         <f>IF(B7 = D7, 1, 0)</f>
@@ -10893,16 +10893,16 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8 = D8, 1, 0)</f>
@@ -10918,16 +10918,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9 = D9, 1, 0)</f>
@@ -10943,10 +10943,10 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -10971,13 +10971,13 @@
         <v>0</v>
       </c>
       <c r="C11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -11021,13 +11021,13 @@
         <v>0</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13 = D13, 1, 0)</f>
@@ -11046,13 +11046,13 @@
         <v>0</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -11121,13 +11121,13 @@
         <v>0</v>
       </c>
       <c r="C17" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17 = D17, 1, 0)</f>
@@ -11196,13 +11196,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -11271,13 +11271,13 @@
         <v>0</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23 = D23, 1, 0)</f>
@@ -11346,13 +11346,13 @@
         <v>0</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26 = D26, 1, 0)</f>
@@ -11396,13 +11396,13 @@
         <v>0</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3">
         <f>IF(B28 = D28, 1, 0)</f>
@@ -11421,13 +11421,13 @@
         <v>0</v>
       </c>
       <c r="C29" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3">
         <f>IF(B29 = D29, 1, 0)</f>
@@ -11446,13 +11446,13 @@
         <v>0</v>
       </c>
       <c r="C30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="3">
         <f>IF(B30 = D30, 1, 0)</f>
@@ -11546,13 +11546,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="3">
         <f>IF(B34 = D34, 1, 0)</f>
@@ -11646,13 +11646,13 @@
         <v>0</v>
       </c>
       <c r="C38" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3">
         <f>IF(B38 = D38, 1, 0)</f>
@@ -11721,13 +11721,13 @@
         <v>0</v>
       </c>
       <c r="C41" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="3">
         <f>IF(B41 = D41, 1, 0)</f>
@@ -11746,13 +11746,13 @@
         <v>0</v>
       </c>
       <c r="C42" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <f>IF(B42 = D42, 1, 0)</f>
@@ -11846,13 +11846,13 @@
         <v>0</v>
       </c>
       <c r="C46" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" s="3">
         <f>IF(B46 = D46, 1, 0)</f>
@@ -11871,13 +11871,13 @@
         <v>0</v>
       </c>
       <c r="C47" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E47" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3">
         <f>IF(B47 = D47, 1, 0)</f>
@@ -11946,13 +11946,13 @@
         <v>0</v>
       </c>
       <c r="C50" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3">
         <f>IF(B50 = D50, 1, 0)</f>
@@ -11996,13 +11996,13 @@
         <v>0</v>
       </c>
       <c r="C52" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52 = D52, 1, 0)</f>
@@ -12077,13 +12077,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3">
         <f>IF(B2 = D2, 1, 0)</f>
@@ -12102,13 +12102,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <f>IF(B3 = D3, 1, 0)</f>
@@ -12177,13 +12177,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3">
         <f>IF(B6 = D6, 1, 0)</f>
@@ -12199,16 +12199,16 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3">
         <f>IF(B7 = D7, 1, 0)</f>
@@ -12224,16 +12224,16 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3">
         <f>IF(B8 = D8, 1, 0)</f>
@@ -12249,16 +12249,16 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3">
         <f>IF(B9 = D9, 1, 0)</f>
@@ -12274,16 +12274,16 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
         <f>IF(B10 = D10, 1, 0)</f>
@@ -12299,16 +12299,16 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3">
         <f>IF(B11 = D11, 1, 0)</f>
@@ -12324,16 +12324,16 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3">
         <f>IF(B12 = D12, 1, 0)</f>
@@ -12349,16 +12349,16 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3">
         <f>IF(B13 = D13, 1, 0)</f>
@@ -12374,16 +12374,16 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3">
         <f>IF(B14 = D14, 1, 0)</f>
@@ -12399,16 +12399,16 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3">
         <f>IF(B15 = D15, 1, 0)</f>
@@ -12424,16 +12424,16 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="3">
         <f>IF(B16 = D16, 1, 0)</f>
@@ -12449,16 +12449,16 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="3">
         <f>IF(B17 = D17, 1, 0)</f>
@@ -12474,16 +12474,16 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3">
         <f>IF(B18 = D18, 1, 0)</f>
@@ -12499,16 +12499,16 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3">
         <f>IF(B19 = D19, 1, 0)</f>
@@ -12527,13 +12527,13 @@
         <v>0</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="3">
         <f>IF(B20 = D20, 1, 0)</f>
@@ -12552,13 +12552,13 @@
         <v>0</v>
       </c>
       <c r="C21" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3">
         <f>IF(B21 = D21, 1, 0)</f>
@@ -12577,13 +12577,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3">
         <f>IF(B22 = D22, 1, 0)</f>
@@ -12602,13 +12602,13 @@
         <v>0</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3">
         <f>IF(B23 = D23, 1, 0)</f>
@@ -12627,13 +12627,13 @@
         <v>0</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3">
         <f>IF(B24 = D24, 1, 0)</f>
@@ -12652,13 +12652,13 @@
         <v>0</v>
       </c>
       <c r="C25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="3">
         <f>IF(B25 = D25, 1, 0)</f>
@@ -12677,13 +12677,13 @@
         <v>0</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="3">
         <f>IF(B26 = D26, 1, 0)</f>
@@ -12752,13 +12752,13 @@
         <v>0</v>
       </c>
       <c r="C29" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3">
         <f>IF(B29 = D29, 1, 0)</f>
@@ -12802,13 +12802,13 @@
         <v>0</v>
       </c>
       <c r="C31" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="3">
         <f>IF(B31 = D31, 1, 0)</f>
@@ -12927,13 +12927,13 @@
         <v>0</v>
       </c>
       <c r="C36" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3">
         <f>IF(B36 = D36, 1, 0)</f>
@@ -13027,13 +13027,13 @@
         <v>0</v>
       </c>
       <c r="C40" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="3">
         <f>IF(B40 = D40, 1, 0)</f>
@@ -13102,13 +13102,13 @@
         <v>0</v>
       </c>
       <c r="C43" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" s="3">
         <f>IF(B43 = D43, 1, 0)</f>
@@ -13152,13 +13152,13 @@
         <v>0</v>
       </c>
       <c r="C45" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" s="3">
         <f>IF(B45 = D45, 1, 0)</f>
@@ -13227,13 +13227,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="3">
         <f>IF(B48 = D48, 1, 0)</f>
@@ -13302,13 +13302,13 @@
         <v>0</v>
       </c>
       <c r="C51" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="3">
         <f>IF(B51 = D51, 1, 0)</f>
@@ -13327,13 +13327,13 @@
         <v>0</v>
       </c>
       <c r="C52" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3">
         <f>IF(B52 = D52, 1, 0)</f>
